--- a/HIMS.xlsx
+++ b/HIMS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{826A6AC5-8979-4EB8-B243-EBC2C04C584D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E10D6165-3B3D-4E25-BD6F-00CC94F928A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51110" yWindow="4090" windowWidth="23130" windowHeight="14810" activeTab="1" xr2:uid="{8C7D3156-1DAC-C540-96E2-F406281F63EC}"/>
+    <workbookView xWindow="9320" yWindow="4780" windowWidth="21060" windowHeight="13820" activeTab="1" xr2:uid="{8C7D3156-1DAC-C540-96E2-F406281F63EC}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -108,7 +108,7 @@
     11/3/25 consensus: 632m</t>
       </text>
     </comment>
-    <comment ref="Z12" authorId="6" shapeId="0" xr:uid="{E0BF3D14-A59E-48D7-8804-F493FD47CAB3}">
+    <comment ref="AD12" authorId="6" shapeId="0" xr:uid="{E0BF3D14-A59E-48D7-8804-F493FD47CAB3}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -116,7 +116,7 @@
     Q3 guidance: 1.460-1.465B</t>
       </text>
     </comment>
-    <comment ref="AA12" authorId="7" shapeId="0" xr:uid="{C25D3745-BEED-4771-AE05-AE0AF8CBF306}">
+    <comment ref="AE12" authorId="7" shapeId="0" xr:uid="{C25D3745-BEED-4771-AE05-AE0AF8CBF306}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -126,7 +126,7 @@
 8/4/25 consensus: 2350m</t>
       </text>
     </comment>
-    <comment ref="AB12" authorId="8" shapeId="0" xr:uid="{D0D34032-D263-4C9B-B026-35176D5F952B}">
+    <comment ref="AF12" authorId="8" shapeId="0" xr:uid="{D0D34032-D263-4C9B-B026-35176D5F952B}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -142,7 +142,7 @@
     Q424 guidance: 55-65m</t>
       </text>
     </comment>
-    <comment ref="AA20" authorId="10" shapeId="0" xr:uid="{46F2731E-6081-40DC-A00B-069DBA20F116}">
+    <comment ref="AE20" authorId="10" shapeId="0" xr:uid="{46F2731E-6081-40DC-A00B-069DBA20F116}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -163,7 +163,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="93">
   <si>
     <t>Price</t>
   </si>
@@ -430,6 +430,18 @@
   </si>
   <si>
     <t>Subscribers y/y</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
   </si>
 </sst>
 </file>
@@ -439,7 +451,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -485,12 +497,6 @@
       <sz val="10"/>
       <color theme="10"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -645,13 +651,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>26</xdr:col>
+      <xdr:col>30</xdr:col>
       <xdr:colOff>39688</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
+      <xdr:col>30</xdr:col>
       <xdr:colOff>39688</xdr:colOff>
       <xdr:row>89</xdr:row>
       <xdr:rowOff>15875</xdr:rowOff>
@@ -1043,21 +1049,21 @@
   <threadedComment ref="R12" dT="2025-11-03T20:49:42.46" personId="{FD0116FB-70B3-F949-9774-5970B644D79B}" id="{1E1F15CC-D601-4277-ABB9-8B7AE1AB2197}">
     <text>11/3/25 consensus: 632m</text>
   </threadedComment>
-  <threadedComment ref="Z12" dT="2024-12-05T21:26:54.64" personId="{FD0116FB-70B3-F949-9774-5970B644D79B}" id="{E0BF3D14-A59E-48D7-8804-F493FD47CAB3}">
+  <threadedComment ref="AD12" dT="2024-12-05T21:26:54.64" personId="{FD0116FB-70B3-F949-9774-5970B644D79B}" id="{E0BF3D14-A59E-48D7-8804-F493FD47CAB3}">
     <text>Q3 guidance: 1.460-1.465B</text>
   </threadedComment>
-  <threadedComment ref="AA12" dT="2025-05-05T17:09:45.80" personId="{FD0116FB-70B3-F949-9774-5970B644D79B}" id="{C25D3745-BEED-4771-AE05-AE0AF8CBF306}">
+  <threadedComment ref="AE12" dT="2025-05-05T17:09:45.80" personId="{FD0116FB-70B3-F949-9774-5970B644D79B}" id="{C25D3745-BEED-4771-AE05-AE0AF8CBF306}">
     <text>Q424, Q125 guidance: 2.3-2.4B
 5/5/25 consensus: 2330m
 8/4/25 consensus: 2350m</text>
   </threadedComment>
-  <threadedComment ref="AB12" dT="2025-05-05T17:09:37.06" personId="{FD0116FB-70B3-F949-9774-5970B644D79B}" id="{D0D34032-D263-4C9B-B026-35176D5F952B}">
+  <threadedComment ref="AF12" dT="2025-05-05T17:09:37.06" personId="{FD0116FB-70B3-F949-9774-5970B644D79B}" id="{D0D34032-D263-4C9B-B026-35176D5F952B}">
     <text>5/5/25 consensus: 2.80B</text>
   </threadedComment>
   <threadedComment ref="O20" dT="2025-05-05T17:19:36.74" personId="{FD0116FB-70B3-F949-9774-5970B644D79B}" id="{19D4C746-88A9-4E41-80F5-3AE1861C2F13}">
     <text>Q424 guidance: 55-65m</text>
   </threadedComment>
-  <threadedComment ref="AA20" dT="2025-05-05T17:19:24.69" personId="{FD0116FB-70B3-F949-9774-5970B644D79B}" id="{46F2731E-6081-40DC-A00B-069DBA20F116}">
+  <threadedComment ref="AE20" dT="2025-05-05T17:19:24.69" personId="{FD0116FB-70B3-F949-9774-5970B644D79B}" id="{46F2731E-6081-40DC-A00B-069DBA20F116}">
     <text>Q424 guidance: 270-320m</text>
   </threadedComment>
   <threadedComment ref="N25" dT="2025-02-24T20:56:49.57" personId="{FD0116FB-70B3-F949-9774-5970B644D79B}" id="{89590535-03FB-4739-A5B9-C52A88D4D0DB}">
@@ -1153,25 +1159,25 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F99DBEF-A602-DE45-8F11-1D484D54BC6E}">
-  <dimension ref="A1:DO82"/>
+  <dimension ref="A1:DS82"/>
   <sheetFormatPr defaultColWidth="10.83203125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.08203125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.08203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="18" width="7.83203125" style="4" customWidth="1"/>
-    <col min="19" max="20" width="8.58203125" style="1" customWidth="1"/>
-    <col min="21" max="26" width="8" style="1" customWidth="1"/>
-    <col min="27" max="32" width="7.5" style="1" customWidth="1"/>
-    <col min="33" max="37" width="9.08203125" style="1" customWidth="1"/>
-    <col min="38" max="16384" width="10.83203125" style="1"/>
+    <col min="3" max="22" width="7.83203125" style="4" customWidth="1"/>
+    <col min="23" max="24" width="8.58203125" style="1" customWidth="1"/>
+    <col min="25" max="30" width="8" style="1" customWidth="1"/>
+    <col min="31" max="36" width="7.5" style="1" customWidth="1"/>
+    <col min="37" max="41" width="9.08203125" style="1" customWidth="1"/>
+    <col min="42" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:42" x14ac:dyDescent="0.25">
       <c r="C2" s="4" t="s">
         <v>36</v>
       </c>
@@ -1220,78 +1226,90 @@
       <c r="R2" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="U2" s="1">
+      <c r="S2" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="T2" s="26" t="s">
+        <v>90</v>
+      </c>
+      <c r="U2" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="V2" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y2" s="1">
         <v>2019</v>
       </c>
-      <c r="V2" s="1">
+      <c r="Z2" s="1">
         <v>2020</v>
       </c>
-      <c r="W2" s="1">
-        <f>+V2+1</f>
+      <c r="AA2" s="1">
+        <f>+Z2+1</f>
         <v>2021</v>
       </c>
-      <c r="X2" s="1">
-        <f t="shared" ref="X2:AL2" si="0">+W2+1</f>
+      <c r="AB2" s="1">
+        <f t="shared" ref="AB2:AP2" si="0">+AA2+1</f>
         <v>2022</v>
       </c>
-      <c r="Y2" s="1">
+      <c r="AC2" s="1">
         <f t="shared" si="0"/>
         <v>2023</v>
       </c>
-      <c r="Z2" s="1">
+      <c r="AD2" s="1">
         <f t="shared" si="0"/>
         <v>2024</v>
       </c>
-      <c r="AA2" s="1">
+      <c r="AE2" s="1">
         <f t="shared" si="0"/>
         <v>2025</v>
       </c>
-      <c r="AB2" s="1">
+      <c r="AF2" s="1">
         <f t="shared" si="0"/>
         <v>2026</v>
       </c>
-      <c r="AC2" s="1">
+      <c r="AG2" s="1">
         <f t="shared" si="0"/>
         <v>2027</v>
       </c>
-      <c r="AD2" s="1">
+      <c r="AH2" s="1">
         <f t="shared" si="0"/>
         <v>2028</v>
       </c>
-      <c r="AE2" s="1">
+      <c r="AI2" s="1">
         <f t="shared" si="0"/>
         <v>2029</v>
       </c>
-      <c r="AF2" s="1">
+      <c r="AJ2" s="1">
         <f t="shared" si="0"/>
         <v>2030</v>
       </c>
-      <c r="AG2" s="1">
+      <c r="AK2" s="1">
         <f t="shared" si="0"/>
         <v>2031</v>
       </c>
-      <c r="AH2" s="1">
+      <c r="AL2" s="1">
         <f t="shared" si="0"/>
         <v>2032</v>
       </c>
-      <c r="AI2" s="1">
+      <c r="AM2" s="1">
         <f t="shared" si="0"/>
         <v>2033</v>
       </c>
-      <c r="AJ2" s="1">
+      <c r="AN2" s="1">
         <f t="shared" si="0"/>
         <v>2034</v>
       </c>
-      <c r="AK2" s="1">
+      <c r="AO2" s="1">
         <f t="shared" si="0"/>
         <v>2035</v>
       </c>
-      <c r="AL2" s="1">
+      <c r="AP2" s="1">
         <f t="shared" si="0"/>
         <v>2036</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:42" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>33</v>
       </c>
@@ -1330,47 +1348,51 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="X3" s="3">
+      <c r="S3" s="5"/>
+      <c r="T3" s="5"/>
+      <c r="U3" s="5"/>
+      <c r="V3" s="5"/>
+      <c r="AB3" s="3">
         <v>1040</v>
       </c>
-      <c r="Y3" s="3">
+      <c r="AC3" s="3">
         <f>+J3</f>
         <v>1537</v>
       </c>
-      <c r="Z3" s="3">
+      <c r="AD3" s="3">
         <f>+N3</f>
         <v>2229</v>
       </c>
-      <c r="AA3" s="3">
-        <f>+Z3*1.3</f>
+      <c r="AE3" s="3">
+        <f>+AD3*1.3</f>
         <v>2897.7000000000003</v>
       </c>
-      <c r="AB3" s="3">
-        <f t="shared" ref="AB3:AF3" si="1">+AA3+500</f>
+      <c r="AF3" s="3">
+        <f t="shared" ref="AF3:AJ3" si="1">+AE3+500</f>
         <v>3397.7000000000003</v>
       </c>
-      <c r="AC3" s="3">
+      <c r="AG3" s="3">
         <f t="shared" si="1"/>
         <v>3897.7000000000003</v>
       </c>
-      <c r="AD3" s="3">
+      <c r="AH3" s="3">
         <f t="shared" si="1"/>
         <v>4397.7000000000007</v>
       </c>
-      <c r="AE3" s="3">
+      <c r="AI3" s="3">
         <f t="shared" si="1"/>
         <v>4897.7000000000007</v>
       </c>
-      <c r="AF3" s="3">
+      <c r="AJ3" s="3">
         <f t="shared" si="1"/>
         <v>5397.7000000000007</v>
       </c>
-      <c r="AG3" s="3"/>
-      <c r="AH3" s="3"/>
-      <c r="AI3" s="3"/>
-      <c r="AJ3" s="3"/>
-    </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AK3" s="3"/>
+      <c r="AL3" s="3"/>
+      <c r="AM3" s="3"/>
+      <c r="AN3" s="3"/>
+    </row>
+    <row r="4" spans="1:42" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>34</v>
       </c>
@@ -1403,18 +1425,18 @@
       <c r="N4" s="5">
         <v>2807</v>
       </c>
-      <c r="X4" s="3">
+      <c r="AB4" s="3">
         <v>6122</v>
       </c>
-      <c r="Y4" s="3">
+      <c r="AC4" s="3">
         <f>SUM(G4:J4)</f>
         <v>8676</v>
       </c>
-      <c r="Z4" s="3">
+      <c r="AD4" s="3">
         <v>10459</v>
       </c>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>35</v>
       </c>
@@ -1446,7 +1468,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>42</v>
       </c>
@@ -1490,45 +1512,45 @@
         <f t="shared" si="2"/>
         <v>247.67540152155536</v>
       </c>
-      <c r="X6" s="2">
+      <c r="AB6" s="2">
         <f>53*12</f>
         <v>636</v>
       </c>
-      <c r="Y6" s="2">
+      <c r="AC6" s="2">
         <f>54*12</f>
         <v>648</v>
       </c>
-      <c r="Z6" s="2">
+      <c r="AD6" s="2">
         <f>64*12</f>
         <v>768</v>
       </c>
-      <c r="AA6" s="2">
-        <f>+Z6*1.1</f>
+      <c r="AE6" s="2">
+        <f>+AD6*1.1</f>
         <v>844.80000000000007</v>
       </c>
-      <c r="AB6" s="2">
-        <f t="shared" ref="AB6:AF6" si="3">+AA6*1.03</f>
+      <c r="AF6" s="2">
+        <f t="shared" ref="AF6:AJ6" si="3">+AE6*1.03</f>
         <v>870.14400000000012</v>
       </c>
-      <c r="AC6" s="2">
+      <c r="AG6" s="2">
         <f t="shared" si="3"/>
         <v>896.24832000000015</v>
       </c>
-      <c r="AD6" s="2">
+      <c r="AH6" s="2">
         <f t="shared" si="3"/>
         <v>923.13576960000023</v>
       </c>
-      <c r="AE6" s="2">
+      <c r="AI6" s="2">
         <f t="shared" si="3"/>
         <v>950.82984268800021</v>
       </c>
-      <c r="AF6" s="2">
+      <c r="AJ6" s="2">
         <f t="shared" si="3"/>
         <v>979.35473796864028</v>
       </c>
-      <c r="AG6" s="2"/>
-    </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AK6" s="2"/>
+    </row>
+    <row r="7" spans="1:42" x14ac:dyDescent="0.25">
       <c r="B7" s="21" t="s">
         <v>84</v>
       </c>
@@ -1560,21 +1582,21 @@
       <c r="O7" s="6">
         <v>84</v>
       </c>
-      <c r="X7" s="2"/>
-      <c r="Y7" s="2"/>
-      <c r="Z7" s="2"/>
-      <c r="AA7" s="2"/>
       <c r="AB7" s="2"/>
       <c r="AC7" s="2"/>
       <c r="AD7" s="2"/>
       <c r="AE7" s="2"/>
       <c r="AF7" s="2"/>
       <c r="AG7" s="2"/>
-    </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AH7" s="2"/>
+      <c r="AI7" s="2"/>
+      <c r="AJ7" s="2"/>
+      <c r="AK7" s="2"/>
+    </row>
+    <row r="8" spans="1:42" x14ac:dyDescent="0.25">
       <c r="G8" s="5"/>
     </row>
-    <row r="9" spans="1:38" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:42" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B9" s="20" t="s">
         <v>81</v>
       </c>
@@ -1612,17 +1634,21 @@
       <c r="P9" s="5"/>
       <c r="Q9" s="5"/>
       <c r="R9" s="5"/>
-      <c r="X9" s="3">
+      <c r="S9" s="5"/>
+      <c r="T9" s="5"/>
+      <c r="U9" s="5"/>
+      <c r="V9" s="5"/>
+      <c r="AB9" s="3">
         <v>502.50700000000001</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AC9" s="3">
         <v>842.38099999999997</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AD9" s="3">
         <v>1437.9369999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:38" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:42" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B10" s="20" t="s">
         <v>82</v>
       </c>
@@ -1660,20 +1686,24 @@
       <c r="P10" s="5"/>
       <c r="Q10" s="5"/>
       <c r="R10" s="5"/>
-      <c r="X10" s="3">
+      <c r="S10" s="5"/>
+      <c r="T10" s="5"/>
+      <c r="U10" s="5"/>
+      <c r="V10" s="5"/>
+      <c r="AB10" s="3">
         <v>24.408999999999999</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AC10" s="3">
         <v>29.619</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AD10" s="3">
         <v>38.576999999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.25">
       <c r="G11" s="5"/>
     </row>
-    <row r="12" spans="1:38" s="7" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:42" s="7" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B12" s="7" t="s">
         <v>8</v>
       </c>
@@ -1722,51 +1752,55 @@
         <f t="shared" si="4"/>
         <v>644.79999999999995</v>
       </c>
-      <c r="U12" s="7">
+      <c r="S12" s="8"/>
+      <c r="T12" s="8"/>
+      <c r="U12" s="8"/>
+      <c r="V12" s="8"/>
+      <c r="Y12" s="7">
         <v>82.558000000000007</v>
       </c>
-      <c r="V12" s="7">
+      <c r="Z12" s="7">
         <v>148.75700000000001</v>
       </c>
-      <c r="W12" s="7">
+      <c r="AA12" s="7">
         <v>271.87799999999999</v>
       </c>
-      <c r="X12" s="7">
+      <c r="AB12" s="7">
         <v>526.91600000000005</v>
       </c>
-      <c r="Y12" s="7">
+      <c r="AC12" s="7">
         <v>872</v>
       </c>
-      <c r="Z12" s="7">
+      <c r="AD12" s="7">
         <f>SUM(K12:N12)</f>
         <v>1476.5140000000001</v>
       </c>
-      <c r="AA12" s="7">
+      <c r="AE12" s="7">
         <f>SUM(O12:R12)</f>
         <v>2370.3999999999996</v>
       </c>
-      <c r="AB12" s="7">
-        <f t="shared" ref="AB12:AF12" si="5">+AB3*AB6/1000</f>
+      <c r="AF12" s="7">
+        <f t="shared" ref="AF12:AJ12" si="5">+AF3*AF6/1000</f>
         <v>2956.4882688000007</v>
       </c>
-      <c r="AC12" s="7">
+      <c r="AG12" s="7">
         <f t="shared" si="5"/>
         <v>3493.3070768640009</v>
       </c>
-      <c r="AD12" s="7">
+      <c r="AH12" s="7">
         <f t="shared" si="5"/>
         <v>4059.6741739699219</v>
       </c>
-      <c r="AE12" s="7">
+      <c r="AI12" s="7">
         <f t="shared" si="5"/>
         <v>4656.8793205330194</v>
       </c>
-      <c r="AF12" s="7">
+      <c r="AJ12" s="7">
         <f t="shared" si="5"/>
         <v>5286.2630691333297</v>
       </c>
     </row>
-    <row r="13" spans="1:38" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:42" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
         <v>16</v>
       </c>
@@ -1814,45 +1848,49 @@
         <f>+R12*0.2</f>
         <v>128.96</v>
       </c>
-      <c r="W13" s="3">
+      <c r="S13" s="5"/>
+      <c r="T13" s="5"/>
+      <c r="U13" s="5"/>
+      <c r="V13" s="5"/>
+      <c r="AA13" s="3">
         <v>67.384</v>
       </c>
-      <c r="X13" s="3">
+      <c r="AB13" s="3">
         <v>118.194</v>
       </c>
-      <c r="Y13" s="3">
+      <c r="AC13" s="3">
         <v>157.05099999999999</v>
       </c>
-      <c r="Z13" s="3">
+      <c r="AD13" s="3">
         <f>SUM(K13:N13)</f>
         <v>303.37900000000002</v>
       </c>
-      <c r="AA13" s="3">
-        <f t="shared" ref="AA13:AF13" si="6">+AA12-AA14</f>
+      <c r="AE13" s="3">
+        <f t="shared" ref="AE13:AJ13" si="6">+AE12-AE14</f>
         <v>521.48799999999983</v>
       </c>
-      <c r="AB13" s="3">
+      <c r="AF13" s="3">
         <f t="shared" si="6"/>
         <v>739.12206719999995</v>
       </c>
-      <c r="AC13" s="3">
+      <c r="AG13" s="3">
         <f t="shared" si="6"/>
         <v>978.12598152192049</v>
       </c>
-      <c r="AD13" s="3">
+      <c r="AH13" s="3">
         <f t="shared" si="6"/>
         <v>1217.9022521909769</v>
       </c>
-      <c r="AE13" s="3">
+      <c r="AI13" s="3">
         <f t="shared" si="6"/>
         <v>1397.0637961599059</v>
       </c>
-      <c r="AF13" s="3">
+      <c r="AJ13" s="3">
         <f t="shared" si="6"/>
         <v>1585.8789207399991</v>
       </c>
     </row>
-    <row r="14" spans="1:38" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:42" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
         <v>17</v>
       </c>
@@ -1904,55 +1942,59 @@
         <v>416.16299999999995</v>
       </c>
       <c r="Q14" s="5">
-        <f t="shared" ref="P14:R14" si="8">+Q12-Q13</f>
+        <f t="shared" ref="Q14:R14" si="8">+Q12-Q13</f>
         <v>475.84</v>
       </c>
       <c r="R14" s="5">
         <f t="shared" si="8"/>
         <v>515.83999999999992</v>
       </c>
-      <c r="W14" s="3">
-        <f>+W12-W13</f>
+      <c r="S14" s="5"/>
+      <c r="T14" s="5"/>
+      <c r="U14" s="5"/>
+      <c r="V14" s="5"/>
+      <c r="AA14" s="3">
+        <f>+AA12-AA13</f>
         <v>204.49399999999997</v>
       </c>
-      <c r="X14" s="3">
-        <f>+X12-X13</f>
+      <c r="AB14" s="3">
+        <f>+AB12-AB13</f>
         <v>408.72200000000004</v>
       </c>
-      <c r="Y14" s="3">
-        <f>+Y12-Y13</f>
+      <c r="AC14" s="3">
+        <f>+AC12-AC13</f>
         <v>714.94900000000007</v>
       </c>
-      <c r="Z14" s="3">
-        <f>+Z12-Z13</f>
+      <c r="AD14" s="3">
+        <f>+AD12-AD13</f>
         <v>1173.1350000000002</v>
       </c>
-      <c r="AA14" s="3">
-        <f>+AA12*0.78</f>
+      <c r="AE14" s="3">
+        <f>+AE12*0.78</f>
         <v>1848.9119999999998</v>
       </c>
-      <c r="AB14" s="3">
-        <f>+AB12*0.75</f>
+      <c r="AF14" s="3">
+        <f>+AF12*0.75</f>
         <v>2217.3662016000007</v>
       </c>
-      <c r="AC14" s="3">
-        <f>+AC12*0.72</f>
+      <c r="AG14" s="3">
+        <f>+AG12*0.72</f>
         <v>2515.1810953420804</v>
       </c>
-      <c r="AD14" s="3">
-        <f>+AD12*0.7</f>
+      <c r="AH14" s="3">
+        <f>+AH12*0.7</f>
         <v>2841.7719217789449</v>
       </c>
-      <c r="AE14" s="3">
-        <f>+AE12*0.7</f>
+      <c r="AI14" s="3">
+        <f>+AI12*0.7</f>
         <v>3259.8155243731135</v>
       </c>
-      <c r="AF14" s="3">
-        <f>+AF12*0.7</f>
+      <c r="AJ14" s="3">
+        <f>+AJ12*0.7</f>
         <v>3700.3841483933306</v>
       </c>
     </row>
-    <row r="15" spans="1:38" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:42" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
         <v>18</v>
       </c>
@@ -1993,52 +2035,56 @@
         <v>217.86199999999999</v>
       </c>
       <c r="Q15" s="5">
-        <f t="shared" ref="P15:R15" si="9">+M15*1.3</f>
+        <f t="shared" ref="Q15:R15" si="9">+M15*1.3</f>
         <v>236.9692</v>
       </c>
       <c r="R15" s="5">
         <f t="shared" si="9"/>
         <v>287.41050000000001</v>
       </c>
-      <c r="W15" s="3">
+      <c r="S15" s="5"/>
+      <c r="T15" s="5"/>
+      <c r="U15" s="5"/>
+      <c r="V15" s="5"/>
+      <c r="AA15" s="3">
         <v>135.90199999999999</v>
       </c>
-      <c r="X15" s="3">
+      <c r="AB15" s="3">
         <v>272.58699999999999</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AC15" s="3">
         <v>446.435</v>
       </c>
-      <c r="Z15" s="3">
-        <f t="shared" ref="Z15:Z18" si="10">SUM(K15:N15)</f>
+      <c r="AD15" s="3">
+        <f t="shared" ref="AD15:AD18" si="10">SUM(K15:N15)</f>
         <v>678.84400000000005</v>
       </c>
-      <c r="AA15" s="3">
-        <f>+Z15*1.4</f>
+      <c r="AE15" s="3">
+        <f>+AD15*1.4</f>
         <v>950.38160000000005</v>
       </c>
-      <c r="AB15" s="3">
-        <f t="shared" ref="AB15:AF15" si="11">+AA15*1.1</f>
+      <c r="AF15" s="3">
+        <f t="shared" ref="AF15:AJ15" si="11">+AE15*1.1</f>
         <v>1045.4197600000002</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AG15" s="3">
         <f t="shared" si="11"/>
         <v>1149.9617360000004</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AH15" s="3">
         <f t="shared" si="11"/>
         <v>1264.9579096000007</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AI15" s="3">
         <f t="shared" si="11"/>
         <v>1391.4537005600009</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AJ15" s="3">
         <f t="shared" si="11"/>
         <v>1530.5990706160012</v>
       </c>
     </row>
-    <row r="16" spans="1:38" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:42" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
         <v>19</v>
       </c>
@@ -2086,45 +2132,49 @@
         <f t="shared" ref="R16:R18" si="13">+N16*1.2</f>
         <v>69.69959999999999</v>
       </c>
-      <c r="W16" s="3">
+      <c r="S16" s="5"/>
+      <c r="T16" s="5"/>
+      <c r="U16" s="5"/>
+      <c r="V16" s="5"/>
+      <c r="AA16" s="3">
         <v>47.593000000000004</v>
       </c>
-      <c r="X16" s="3">
+      <c r="AB16" s="3">
         <v>77.403000000000006</v>
       </c>
-      <c r="Y16" s="3">
+      <c r="AC16" s="3">
         <v>119.857</v>
       </c>
-      <c r="Z16" s="3">
+      <c r="AD16" s="3">
         <f t="shared" si="10"/>
         <v>185.80199999999999</v>
       </c>
-      <c r="AA16" s="3">
-        <f>+Z16*1.4</f>
+      <c r="AE16" s="3">
+        <f>+AD16*1.4</f>
         <v>260.12279999999998</v>
       </c>
-      <c r="AB16" s="3">
-        <f t="shared" ref="AB16:AF16" si="14">+AA16*1.1</f>
+      <c r="AF16" s="3">
+        <f t="shared" ref="AF16:AJ16" si="14">+AE16*1.1</f>
         <v>286.13508000000002</v>
       </c>
-      <c r="AC16" s="3">
+      <c r="AG16" s="3">
         <f t="shared" si="14"/>
         <v>314.74858800000004</v>
       </c>
-      <c r="AD16" s="3">
+      <c r="AH16" s="3">
         <f t="shared" si="14"/>
         <v>346.22344680000009</v>
       </c>
-      <c r="AE16" s="3">
+      <c r="AI16" s="3">
         <f t="shared" si="14"/>
         <v>380.84579148000012</v>
       </c>
-      <c r="AF16" s="3">
+      <c r="AJ16" s="3">
         <f t="shared" si="14"/>
         <v>418.93037062800016</v>
       </c>
     </row>
-    <row r="17" spans="2:119" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:123" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
         <v>20</v>
       </c>
@@ -2172,45 +2222,49 @@
         <f t="shared" si="13"/>
         <v>28.498799999999999</v>
       </c>
-      <c r="W17" s="3">
+      <c r="S17" s="5"/>
+      <c r="T17" s="5"/>
+      <c r="U17" s="5"/>
+      <c r="V17" s="5"/>
+      <c r="AA17" s="3">
         <v>22.379000000000001</v>
       </c>
-      <c r="X17" s="3">
+      <c r="AB17" s="3">
         <v>29.236999999999998</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AC17" s="3">
         <v>48.226999999999997</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AD17" s="3">
         <f t="shared" si="10"/>
         <v>78.819000000000003</v>
       </c>
-      <c r="AA17" s="3">
-        <f t="shared" ref="AA17:AF17" si="15">+Z17*1.1</f>
+      <c r="AE17" s="3">
+        <f t="shared" ref="AE17:AJ17" si="15">+AD17*1.1</f>
         <v>86.700900000000004</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AF17" s="3">
         <f t="shared" si="15"/>
         <v>95.370990000000006</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AG17" s="3">
         <f t="shared" si="15"/>
         <v>104.90808900000002</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AH17" s="3">
         <f t="shared" si="15"/>
         <v>115.39889790000002</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AI17" s="3">
         <f t="shared" si="15"/>
         <v>126.93878769000004</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AJ17" s="3">
         <f t="shared" si="15"/>
         <v>139.63266645900006</v>
       </c>
     </row>
-    <row r="18" spans="2:119" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:123" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B18" s="3" t="s">
         <v>21</v>
       </c>
@@ -2258,45 +2312,49 @@
         <f t="shared" si="13"/>
         <v>57.633599999999994</v>
       </c>
-      <c r="W18" s="3">
+      <c r="S18" s="5"/>
+      <c r="T18" s="5"/>
+      <c r="U18" s="5"/>
+      <c r="V18" s="5"/>
+      <c r="AA18" s="3">
         <v>113.66200000000001</v>
       </c>
-      <c r="X18" s="3">
+      <c r="AB18" s="3">
         <v>98.191999999999993</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AC18" s="3">
         <v>129.88300000000001</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AD18" s="3">
         <f t="shared" si="10"/>
         <v>167.767</v>
       </c>
-      <c r="AA18" s="3">
-        <f t="shared" ref="AA18:AF18" si="16">+Z18*1.1</f>
+      <c r="AE18" s="3">
+        <f t="shared" ref="AE18:AJ18" si="16">+AD18*1.1</f>
         <v>184.5437</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AF18" s="3">
         <f t="shared" si="16"/>
         <v>202.99807000000001</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AG18" s="3">
         <f t="shared" si="16"/>
         <v>223.29787700000003</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AH18" s="3">
         <f t="shared" si="16"/>
         <v>245.62766470000005</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AI18" s="3">
         <f t="shared" si="16"/>
         <v>270.19043117000007</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AJ18" s="3">
         <f t="shared" si="16"/>
         <v>297.20947428700009</v>
       </c>
     </row>
-    <row r="19" spans="2:119" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:123" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B19" s="3" t="s">
         <v>22</v>
       </c>
@@ -2355,48 +2413,52 @@
         <f t="shared" si="18"/>
         <v>443.24250000000001</v>
       </c>
-      <c r="W19" s="3">
-        <f>SUM(W15:W18)</f>
+      <c r="S19" s="5"/>
+      <c r="T19" s="5"/>
+      <c r="U19" s="5"/>
+      <c r="V19" s="5"/>
+      <c r="AA19" s="3">
+        <f>SUM(AA15:AA18)</f>
         <v>319.536</v>
       </c>
-      <c r="X19" s="3">
-        <f>SUM(X15:X18)</f>
+      <c r="AB19" s="3">
+        <f>SUM(AB15:AB18)</f>
         <v>477.41900000000004</v>
       </c>
-      <c r="Y19" s="3">
-        <f>SUM(Y15:Y18)</f>
+      <c r="AC19" s="3">
+        <f>SUM(AC15:AC18)</f>
         <v>744.40200000000004</v>
       </c>
-      <c r="Z19" s="3">
-        <f t="shared" ref="Z19" si="19">SUM(Z15:Z18)</f>
+      <c r="AD19" s="3">
+        <f t="shared" ref="AD19" si="19">SUM(AD15:AD18)</f>
         <v>1111.232</v>
       </c>
-      <c r="AA19" s="3">
-        <f t="shared" ref="AA19" si="20">SUM(AA15:AA18)</f>
+      <c r="AE19" s="3">
+        <f t="shared" ref="AE19" si="20">SUM(AE15:AE18)</f>
         <v>1481.749</v>
       </c>
-      <c r="AB19" s="3">
-        <f t="shared" ref="AB19" si="21">SUM(AB15:AB18)</f>
+      <c r="AF19" s="3">
+        <f t="shared" ref="AF19" si="21">SUM(AF15:AF18)</f>
         <v>1629.9239000000002</v>
       </c>
-      <c r="AC19" s="3">
-        <f t="shared" ref="AC19" si="22">SUM(AC15:AC18)</f>
+      <c r="AG19" s="3">
+        <f t="shared" ref="AG19" si="22">SUM(AG15:AG18)</f>
         <v>1792.9162900000006</v>
       </c>
-      <c r="AD19" s="3">
-        <f t="shared" ref="AD19" si="23">SUM(AD15:AD18)</f>
+      <c r="AH19" s="3">
+        <f t="shared" ref="AH19" si="23">SUM(AH15:AH18)</f>
         <v>1972.2079190000009</v>
       </c>
-      <c r="AE19" s="3">
-        <f t="shared" ref="AE19" si="24">SUM(AE15:AE18)</f>
+      <c r="AI19" s="3">
+        <f t="shared" ref="AI19" si="24">SUM(AI15:AI18)</f>
         <v>2169.4287109000011</v>
       </c>
-      <c r="AF19" s="3">
-        <f t="shared" ref="AF19" si="25">SUM(AF15:AF18)</f>
+      <c r="AJ19" s="3">
+        <f t="shared" ref="AJ19" si="25">SUM(AJ15:AJ18)</f>
         <v>2386.3715819900012</v>
       </c>
     </row>
-    <row r="20" spans="2:119" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:123" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20" s="3" t="s">
         <v>23</v>
       </c>
@@ -2455,48 +2517,52 @@
         <f t="shared" si="27"/>
         <v>72.597499999999911</v>
       </c>
-      <c r="W20" s="3">
-        <f>W14-W19</f>
+      <c r="S20" s="5"/>
+      <c r="T20" s="5"/>
+      <c r="U20" s="5"/>
+      <c r="V20" s="5"/>
+      <c r="AA20" s="3">
+        <f>AA14-AA19</f>
         <v>-115.04200000000003</v>
       </c>
-      <c r="X20" s="3">
-        <f>X14-X19</f>
+      <c r="AB20" s="3">
+        <f>AB14-AB19</f>
         <v>-68.697000000000003</v>
       </c>
-      <c r="Y20" s="3">
-        <f>Y14-Y19</f>
+      <c r="AC20" s="3">
+        <f>AC14-AC19</f>
         <v>-29.452999999999975</v>
       </c>
-      <c r="Z20" s="3">
-        <f t="shared" ref="Z20" si="28">Z14-Z19</f>
+      <c r="AD20" s="3">
+        <f t="shared" ref="AD20" si="28">AD14-AD19</f>
         <v>61.903000000000247</v>
       </c>
-      <c r="AA20" s="3">
-        <f t="shared" ref="AA20" si="29">AA14-AA19</f>
+      <c r="AE20" s="3">
+        <f t="shared" ref="AE20" si="29">AE14-AE19</f>
         <v>367.16299999999978</v>
       </c>
-      <c r="AB20" s="3">
-        <f t="shared" ref="AB20" si="30">AB14-AB19</f>
+      <c r="AF20" s="3">
+        <f t="shared" ref="AF20" si="30">AF14-AF19</f>
         <v>587.44230160000052</v>
       </c>
-      <c r="AC20" s="3">
-        <f t="shared" ref="AC20" si="31">AC14-AC19</f>
+      <c r="AG20" s="3">
+        <f t="shared" ref="AG20" si="31">AG14-AG19</f>
         <v>722.26480534207985</v>
       </c>
-      <c r="AD20" s="3">
-        <f t="shared" ref="AD20" si="32">AD14-AD19</f>
+      <c r="AH20" s="3">
+        <f t="shared" ref="AH20" si="32">AH14-AH19</f>
         <v>869.56400277894409</v>
       </c>
-      <c r="AE20" s="3">
-        <f t="shared" ref="AE20" si="33">AE14-AE19</f>
+      <c r="AI20" s="3">
+        <f t="shared" ref="AI20" si="33">AI14-AI19</f>
         <v>1090.3868134731124</v>
       </c>
-      <c r="AF20" s="3">
-        <f t="shared" ref="AF20" si="34">AF14-AF19</f>
+      <c r="AJ20" s="3">
+        <f t="shared" ref="AJ20" si="34">AJ14-AJ19</f>
         <v>1314.0125664033294</v>
       </c>
     </row>
-    <row r="21" spans="2:119" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:123" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
         <v>24</v>
       </c>
@@ -2542,21 +2608,25 @@
         <f>+Q21</f>
         <v>6.13</v>
       </c>
-      <c r="W21" s="3">
+      <c r="S21" s="5"/>
+      <c r="T21" s="5"/>
+      <c r="U21" s="5"/>
+      <c r="V21" s="5"/>
+      <c r="AA21" s="3">
         <v>4.2469999999999999</v>
       </c>
-      <c r="X21" s="3">
+      <c r="AB21" s="3">
         <v>2.988</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AC21" s="3">
         <v>7.8819999999999997</v>
       </c>
-      <c r="Z21" s="3">
-        <f t="shared" ref="Z21" si="35">SUM(K21:N21)</f>
+      <c r="AD21" s="3">
+        <f t="shared" ref="AD21" si="35">SUM(K21:N21)</f>
         <v>9.8079999999999998</v>
       </c>
     </row>
-    <row r="22" spans="2:119" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:123" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
         <v>25</v>
       </c>
@@ -2614,48 +2684,52 @@
         <f t="shared" si="36"/>
         <v>78.727499999999907</v>
       </c>
-      <c r="W22" s="3">
-        <f>+W20+W21</f>
+      <c r="S22" s="5"/>
+      <c r="T22" s="5"/>
+      <c r="U22" s="5"/>
+      <c r="V22" s="5"/>
+      <c r="AA22" s="3">
+        <f>+AA20+AA21</f>
         <v>-110.79500000000003</v>
       </c>
-      <c r="X22" s="3">
-        <f>+X20+X21</f>
+      <c r="AB22" s="3">
+        <f>+AB20+AB21</f>
         <v>-65.709000000000003</v>
       </c>
-      <c r="Y22" s="3">
-        <f>+Y20+Y21</f>
+      <c r="AC22" s="3">
+        <f>+AC20+AC21</f>
         <v>-21.570999999999977</v>
       </c>
-      <c r="Z22" s="3">
-        <f>+Z20+Z21</f>
+      <c r="AD22" s="3">
+        <f>+AD20+AD21</f>
         <v>71.71100000000024</v>
       </c>
-      <c r="AA22" s="3">
-        <f t="shared" ref="AA22:AF22" si="37">+AA20+AA21</f>
+      <c r="AE22" s="3">
+        <f t="shared" ref="AE22:AJ22" si="37">+AE20+AE21</f>
         <v>367.16299999999978</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AF22" s="3">
         <f t="shared" si="37"/>
         <v>587.44230160000052</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AG22" s="3">
         <f t="shared" si="37"/>
         <v>722.26480534207985</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AH22" s="3">
         <f t="shared" si="37"/>
         <v>869.56400277894409</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AI22" s="3">
         <f t="shared" si="37"/>
         <v>1090.3868134731124</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AJ22" s="3">
         <f t="shared" si="37"/>
         <v>1314.0125664033294</v>
       </c>
     </row>
-    <row r="23" spans="2:119" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:123" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
         <v>27</v>
       </c>
@@ -2703,45 +2777,49 @@
         <f>+R22*0.1</f>
         <v>7.872749999999991</v>
       </c>
-      <c r="W23" s="3">
+      <c r="S23" s="5"/>
+      <c r="T23" s="5"/>
+      <c r="U23" s="5"/>
+      <c r="V23" s="5"/>
+      <c r="AA23" s="3">
         <v>-3.1360000000000001</v>
       </c>
-      <c r="X23" s="3">
+      <c r="AB23" s="3">
         <v>3.1E-2</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AC23" s="3">
         <v>1.9750000000000001</v>
       </c>
-      <c r="Z23" s="3">
-        <f t="shared" ref="Z23" si="38">SUM(K23:N23)</f>
+      <c r="AD23" s="3">
+        <f t="shared" ref="AD23" si="38">SUM(K23:N23)</f>
         <v>1.1479999999999999</v>
       </c>
-      <c r="AA23" s="3">
-        <f t="shared" ref="AA23:AF23" si="39">+AA22*0.2</f>
+      <c r="AE23" s="3">
+        <f t="shared" ref="AE23:AJ23" si="39">+AE22*0.2</f>
         <v>73.432599999999965</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AF23" s="3">
         <f t="shared" si="39"/>
         <v>117.48846032000012</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AG23" s="3">
         <f t="shared" si="39"/>
         <v>144.45296106841599</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AH23" s="3">
         <f t="shared" si="39"/>
         <v>173.91280055578883</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AI23" s="3">
         <f t="shared" si="39"/>
         <v>218.07736269462248</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AJ23" s="3">
         <f t="shared" si="39"/>
         <v>262.80251328066589</v>
       </c>
     </row>
-    <row r="24" spans="2:119" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:123" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
         <v>26</v>
       </c>
@@ -2799,396 +2877,400 @@
         <f t="shared" si="40"/>
         <v>86.600249999999903</v>
       </c>
-      <c r="W24" s="3">
-        <f>+W22-W23</f>
+      <c r="S24" s="5"/>
+      <c r="T24" s="5"/>
+      <c r="U24" s="5"/>
+      <c r="V24" s="5"/>
+      <c r="AA24" s="3">
+        <f>+AA22-AA23</f>
         <v>-107.65900000000003</v>
       </c>
-      <c r="X24" s="3">
-        <f>+X22-X23</f>
+      <c r="AB24" s="3">
+        <f>+AB22-AB23</f>
         <v>-65.740000000000009</v>
       </c>
-      <c r="Y24" s="3">
-        <f>+Y22-Y23</f>
+      <c r="AC24" s="3">
+        <f>+AC22-AC23</f>
         <v>-23.545999999999978</v>
       </c>
-      <c r="Z24" s="3">
-        <f>+Z22-Z23</f>
+      <c r="AD24" s="3">
+        <f>+AD22-AD23</f>
         <v>70.563000000000244</v>
       </c>
-      <c r="AA24" s="3">
-        <f t="shared" ref="AA24:AF24" si="41">+AA22-AA23</f>
+      <c r="AE24" s="3">
+        <f t="shared" ref="AE24:AJ24" si="41">+AE22-AE23</f>
         <v>293.7303999999998</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AF24" s="3">
         <f t="shared" si="41"/>
         <v>469.9538412800004</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AG24" s="3">
         <f t="shared" si="41"/>
         <v>577.81184427366384</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AH24" s="3">
         <f t="shared" si="41"/>
         <v>695.65120222315522</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AI24" s="3">
         <f t="shared" si="41"/>
         <v>872.30945077848992</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AJ24" s="3">
         <f t="shared" si="41"/>
         <v>1051.2100531226636</v>
       </c>
-      <c r="AG24" s="3">
-        <f>+AF24*(1+$AH$78)</f>
+      <c r="AK24" s="3">
+        <f>+AJ24*(1+$AL$78)</f>
         <v>1040.6979525914369</v>
       </c>
-      <c r="AH24" s="3">
-        <f t="shared" ref="AH24:CS24" si="42">+AG24*(1+$AH$78)</f>
+      <c r="AL24" s="3">
+        <f t="shared" ref="AL24:CW24" si="42">+AK24*(1+$AL$78)</f>
         <v>1030.2909730655226</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AM24" s="3">
         <f t="shared" si="42"/>
         <v>1019.9880633348674</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AN24" s="3">
         <f t="shared" si="42"/>
         <v>1009.7881827015187</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AO24" s="3">
         <f t="shared" si="42"/>
         <v>999.69030087450358</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AP24" s="3">
         <f t="shared" si="42"/>
         <v>989.69339786575858</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AQ24" s="3">
         <f t="shared" si="42"/>
         <v>979.79646388710103</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AR24" s="3">
         <f t="shared" si="42"/>
         <v>969.99849924823002</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AS24" s="3">
         <f t="shared" si="42"/>
         <v>960.2985142557477</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AT24" s="3">
         <f t="shared" si="42"/>
         <v>950.69552911319022</v>
       </c>
-      <c r="AQ24" s="3">
+      <c r="AU24" s="3">
         <f t="shared" si="42"/>
         <v>941.18857382205829</v>
       </c>
-      <c r="AR24" s="3">
+      <c r="AV24" s="3">
         <f t="shared" si="42"/>
         <v>931.77668808383771</v>
       </c>
-      <c r="AS24" s="3">
+      <c r="AW24" s="3">
         <f t="shared" si="42"/>
         <v>922.45892120299936</v>
       </c>
-      <c r="AT24" s="3">
+      <c r="AX24" s="3">
         <f t="shared" si="42"/>
         <v>913.23433199096939</v>
       </c>
-      <c r="AU24" s="3">
+      <c r="AY24" s="3">
         <f t="shared" si="42"/>
         <v>904.10198867105964</v>
       </c>
-      <c r="AV24" s="3">
+      <c r="AZ24" s="3">
         <f t="shared" si="42"/>
         <v>895.06096878434903</v>
       </c>
-      <c r="AW24" s="3">
+      <c r="BA24" s="3">
         <f t="shared" si="42"/>
         <v>886.11035909650548</v>
       </c>
-      <c r="AX24" s="3">
+      <c r="BB24" s="3">
         <f t="shared" si="42"/>
         <v>877.24925550554042</v>
       </c>
-      <c r="AY24" s="3">
+      <c r="BC24" s="3">
         <f t="shared" si="42"/>
         <v>868.47676295048495</v>
       </c>
-      <c r="AZ24" s="3">
+      <c r="BD24" s="3">
         <f t="shared" si="42"/>
         <v>859.79199532098005</v>
       </c>
-      <c r="BA24" s="3">
+      <c r="BE24" s="3">
         <f t="shared" si="42"/>
         <v>851.19407536777021</v>
       </c>
-      <c r="BB24" s="3">
+      <c r="BF24" s="3">
         <f t="shared" si="42"/>
         <v>842.68213461409255</v>
       </c>
-      <c r="BC24" s="3">
+      <c r="BG24" s="3">
         <f t="shared" si="42"/>
         <v>834.25531326795158</v>
       </c>
-      <c r="BD24" s="3">
+      <c r="BH24" s="3">
         <f t="shared" si="42"/>
         <v>825.91276013527204</v>
       </c>
-      <c r="BE24" s="3">
+      <c r="BI24" s="3">
         <f t="shared" si="42"/>
         <v>817.65363253391934</v>
       </c>
-      <c r="BF24" s="3">
+      <c r="BJ24" s="3">
         <f t="shared" si="42"/>
         <v>809.47709620858018</v>
       </c>
-      <c r="BG24" s="3">
+      <c r="BK24" s="3">
         <f t="shared" si="42"/>
         <v>801.38232524649436</v>
       </c>
-      <c r="BH24" s="3">
+      <c r="BL24" s="3">
         <f t="shared" si="42"/>
         <v>793.36850199402943</v>
       </c>
-      <c r="BI24" s="3">
+      <c r="BM24" s="3">
         <f t="shared" si="42"/>
         <v>785.43481697408913</v>
       </c>
-      <c r="BJ24" s="3">
+      <c r="BN24" s="3">
         <f t="shared" si="42"/>
         <v>777.58046880434824</v>
       </c>
-      <c r="BK24" s="3">
+      <c r="BO24" s="3">
         <f t="shared" si="42"/>
         <v>769.80466411630471</v>
       </c>
-      <c r="BL24" s="3">
+      <c r="BP24" s="3">
         <f t="shared" si="42"/>
         <v>762.10661747514166</v>
       </c>
-      <c r="BM24" s="3">
+      <c r="BQ24" s="3">
         <f t="shared" si="42"/>
         <v>754.48555130039028</v>
       </c>
-      <c r="BN24" s="3">
+      <c r="BR24" s="3">
         <f t="shared" si="42"/>
         <v>746.9406957873864</v>
       </c>
-      <c r="BO24" s="3">
+      <c r="BS24" s="3">
         <f t="shared" si="42"/>
         <v>739.47128882951256</v>
       </c>
-      <c r="BP24" s="3">
+      <c r="BT24" s="3">
         <f t="shared" si="42"/>
         <v>732.07657594121747</v>
       </c>
-      <c r="BQ24" s="3">
+      <c r="BU24" s="3">
         <f t="shared" si="42"/>
         <v>724.75581018180526</v>
       </c>
-      <c r="BR24" s="3">
+      <c r="BV24" s="3">
         <f t="shared" si="42"/>
         <v>717.50825207998719</v>
       </c>
-      <c r="BS24" s="3">
+      <c r="BW24" s="3">
         <f t="shared" si="42"/>
         <v>710.33316955918735</v>
       </c>
-      <c r="BT24" s="3">
+      <c r="BX24" s="3">
         <f t="shared" si="42"/>
         <v>703.22983786359544</v>
       </c>
-      <c r="BU24" s="3">
+      <c r="BY24" s="3">
         <f t="shared" si="42"/>
         <v>696.19753948495952</v>
       </c>
-      <c r="BV24" s="3">
+      <c r="BZ24" s="3">
         <f t="shared" si="42"/>
         <v>689.23556409010996</v>
       </c>
-      <c r="BW24" s="3">
+      <c r="CA24" s="3">
         <f t="shared" si="42"/>
         <v>682.34320844920887</v>
       </c>
-      <c r="BX24" s="3">
+      <c r="CB24" s="3">
         <f t="shared" si="42"/>
         <v>675.51977636471679</v>
       </c>
-      <c r="BY24" s="3">
+      <c r="CC24" s="3">
         <f t="shared" si="42"/>
         <v>668.76457860106962</v>
       </c>
-      <c r="BZ24" s="3">
+      <c r="CD24" s="3">
         <f t="shared" si="42"/>
         <v>662.07693281505897</v>
       </c>
-      <c r="CA24" s="3">
+      <c r="CE24" s="3">
         <f t="shared" si="42"/>
         <v>655.45616348690839</v>
       </c>
-      <c r="CB24" s="3">
+      <c r="CF24" s="3">
         <f t="shared" si="42"/>
         <v>648.90160185203933</v>
       </c>
-      <c r="CC24" s="3">
+      <c r="CG24" s="3">
         <f t="shared" si="42"/>
         <v>642.41258583351896</v>
       </c>
-      <c r="CD24" s="3">
+      <c r="CH24" s="3">
         <f t="shared" si="42"/>
         <v>635.98845997518379</v>
       </c>
-      <c r="CE24" s="3">
+      <c r="CI24" s="3">
         <f t="shared" si="42"/>
         <v>629.62857537543198</v>
       </c>
-      <c r="CF24" s="3">
+      <c r="CJ24" s="3">
         <f t="shared" si="42"/>
         <v>623.33228962167766</v>
       </c>
-      <c r="CG24" s="3">
+      <c r="CK24" s="3">
         <f t="shared" si="42"/>
         <v>617.09896672546085</v>
       </c>
-      <c r="CH24" s="3">
+      <c r="CL24" s="3">
         <f t="shared" si="42"/>
         <v>610.92797705820624</v>
       </c>
-      <c r="CI24" s="3">
+      <c r="CM24" s="3">
         <f t="shared" si="42"/>
         <v>604.81869728762422</v>
       </c>
-      <c r="CJ24" s="3">
+      <c r="CN24" s="3">
         <f t="shared" si="42"/>
         <v>598.77051031474798</v>
       </c>
-      <c r="CK24" s="3">
+      <c r="CO24" s="3">
         <f t="shared" si="42"/>
         <v>592.78280521160048</v>
       </c>
-      <c r="CL24" s="3">
+      <c r="CP24" s="3">
         <f t="shared" si="42"/>
         <v>586.85497715948452</v>
       </c>
-      <c r="CM24" s="3">
+      <c r="CQ24" s="3">
         <f t="shared" si="42"/>
         <v>580.98642738788965</v>
       </c>
-      <c r="CN24" s="3">
+      <c r="CR24" s="3">
         <f t="shared" si="42"/>
         <v>575.17656311401072</v>
       </c>
-      <c r="CO24" s="3">
+      <c r="CS24" s="3">
         <f t="shared" si="42"/>
         <v>569.42479748287064</v>
       </c>
-      <c r="CP24" s="3">
+      <c r="CT24" s="3">
         <f t="shared" si="42"/>
         <v>563.73054950804192</v>
       </c>
-      <c r="CQ24" s="3">
+      <c r="CU24" s="3">
         <f t="shared" si="42"/>
         <v>558.09324401296146</v>
       </c>
-      <c r="CR24" s="3">
+      <c r="CV24" s="3">
         <f t="shared" si="42"/>
         <v>552.51231157283189</v>
       </c>
-      <c r="CS24" s="3">
+      <c r="CW24" s="3">
         <f t="shared" si="42"/>
         <v>546.98718845710357</v>
       </c>
-      <c r="CT24" s="3">
-        <f t="shared" ref="CT24:DO24" si="43">+CS24*(1+$AH$78)</f>
+      <c r="CX24" s="3">
+        <f t="shared" ref="CX24:DS24" si="43">+CW24*(1+$AL$78)</f>
         <v>541.51731657253254</v>
       </c>
-      <c r="CU24" s="3">
+      <c r="CY24" s="3">
         <f t="shared" si="43"/>
         <v>536.10214340680716</v>
       </c>
-      <c r="CV24" s="3">
+      <c r="CZ24" s="3">
         <f t="shared" si="43"/>
         <v>530.74112197273905</v>
       </c>
-      <c r="CW24" s="3">
+      <c r="DA24" s="3">
         <f t="shared" si="43"/>
         <v>525.43371075301161</v>
       </c>
-      <c r="CX24" s="3">
+      <c r="DB24" s="3">
         <f t="shared" si="43"/>
         <v>520.17937364548152</v>
       </c>
-      <c r="CY24" s="3">
+      <c r="DC24" s="3">
         <f t="shared" si="43"/>
         <v>514.97757990902664</v>
       </c>
-      <c r="CZ24" s="3">
+      <c r="DD24" s="3">
         <f t="shared" si="43"/>
         <v>509.82780410993638</v>
       </c>
-      <c r="DA24" s="3">
+      <c r="DE24" s="3">
         <f t="shared" si="43"/>
         <v>504.729526068837</v>
       </c>
-      <c r="DB24" s="3">
+      <c r="DF24" s="3">
         <f t="shared" si="43"/>
         <v>499.68223080814863</v>
       </c>
-      <c r="DC24" s="3">
+      <c r="DG24" s="3">
         <f t="shared" si="43"/>
         <v>494.68540850006713</v>
       </c>
-      <c r="DD24" s="3">
+      <c r="DH24" s="3">
         <f t="shared" si="43"/>
         <v>489.73855441506646</v>
       </c>
-      <c r="DE24" s="3">
+      <c r="DI24" s="3">
         <f t="shared" si="43"/>
         <v>484.84116887091579</v>
       </c>
-      <c r="DF24" s="3">
+      <c r="DJ24" s="3">
         <f t="shared" si="43"/>
         <v>479.99275718220662</v>
       </c>
-      <c r="DG24" s="3">
+      <c r="DK24" s="3">
         <f t="shared" si="43"/>
         <v>475.19282961038454</v>
       </c>
-      <c r="DH24" s="3">
+      <c r="DL24" s="3">
         <f t="shared" si="43"/>
         <v>470.44090131428067</v>
       </c>
-      <c r="DI24" s="3">
+      <c r="DM24" s="3">
         <f t="shared" si="43"/>
         <v>465.73649230113784</v>
       </c>
-      <c r="DJ24" s="3">
+      <c r="DN24" s="3">
         <f t="shared" si="43"/>
         <v>461.07912737812649</v>
       </c>
-      <c r="DK24" s="3">
+      <c r="DO24" s="3">
         <f t="shared" si="43"/>
         <v>456.46833610434521</v>
       </c>
-      <c r="DL24" s="3">
+      <c r="DP24" s="3">
         <f t="shared" si="43"/>
         <v>451.90365274330173</v>
       </c>
-      <c r="DM24" s="3">
+      <c r="DQ24" s="3">
         <f t="shared" si="43"/>
         <v>447.38461621586873</v>
       </c>
-      <c r="DN24" s="3">
+      <c r="DR24" s="3">
         <f t="shared" si="43"/>
         <v>442.91077005371005</v>
       </c>
-      <c r="DO24" s="3">
+      <c r="DS24" s="3">
         <f t="shared" si="43"/>
         <v>438.48166235317296</v>
       </c>
     </row>
-    <row r="25" spans="2:119" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:123" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
         <v>28</v>
       </c>
@@ -3246,48 +3328,52 @@
         <f t="shared" si="45"/>
         <v>0.33725558367845293</v>
       </c>
-      <c r="W25" s="2">
-        <f>+W24/W26</f>
-        <v>-0.57638994586493864</v>
-      </c>
-      <c r="X25" s="2">
-        <f>+X24/X26</f>
-        <v>-0.32144165457471036</v>
-      </c>
-      <c r="Y25" s="2">
-        <f>+Y24/Y26</f>
-        <v>-0.11247477796334296</v>
-      </c>
-      <c r="Z25" s="2">
-        <f>+Z24/Z26</f>
-        <v>0.30028359155938178</v>
-      </c>
+      <c r="S25" s="6"/>
+      <c r="T25" s="6"/>
+      <c r="U25" s="6"/>
+      <c r="V25" s="6"/>
       <c r="AA25" s="2">
         <f>+AA24/AA26</f>
+        <v>-0.57638994586493864</v>
+      </c>
+      <c r="AB25" s="2">
+        <f>+AB24/AB26</f>
+        <v>-0.32144165457471036</v>
+      </c>
+      <c r="AC25" s="2">
+        <f>+AC24/AC26</f>
+        <v>-0.11247477796334296</v>
+      </c>
+      <c r="AD25" s="2">
+        <f>+AD24/AD26</f>
+        <v>0.30028359155938178</v>
+      </c>
+      <c r="AE25" s="2">
+        <f>+AE24/AE26</f>
         <v>1.2499811439730946</v>
       </c>
-      <c r="AB25" s="2">
-        <f t="shared" ref="AB25:AF25" si="46">+AB24/AB26</f>
+      <c r="AF25" s="2">
+        <f t="shared" ref="AF25:AJ25" si="46">+AF24/AF26</f>
         <v>1.9999068538282909</v>
       </c>
-      <c r="AC25" s="2">
+      <c r="AG25" s="2">
         <f t="shared" si="46"/>
         <v>2.4589007814866912</v>
       </c>
-      <c r="AD25" s="2">
+      <c r="AH25" s="2">
         <f t="shared" si="46"/>
         <v>2.9603707534567709</v>
       </c>
-      <c r="AE25" s="2">
+      <c r="AI25" s="2">
         <f t="shared" si="46"/>
         <v>3.7121468025871325</v>
       </c>
-      <c r="AF25" s="2">
+      <c r="AJ25" s="2">
         <f t="shared" si="46"/>
         <v>4.4734652754985031</v>
       </c>
     </row>
-    <row r="26" spans="2:119" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:123" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
         <v>1</v>
       </c>
@@ -3328,52 +3414,56 @@
         <v>256.779292</v>
       </c>
       <c r="Q26" s="5">
-        <f t="shared" ref="P26:R26" si="47">+P26</f>
+        <f t="shared" ref="Q26:R26" si="47">+P26</f>
         <v>256.779292</v>
       </c>
       <c r="R26" s="5">
         <f t="shared" si="47"/>
         <v>256.779292</v>
       </c>
-      <c r="W26" s="3">
+      <c r="S26" s="5"/>
+      <c r="T26" s="5"/>
+      <c r="U26" s="5"/>
+      <c r="V26" s="5"/>
+      <c r="AA26" s="3">
         <v>186.78153699999999</v>
       </c>
-      <c r="X26" s="3">
+      <c r="AB26" s="3">
         <v>204.51612</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AC26" s="3">
         <v>209.34471199999999</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AD26" s="3">
         <f>AVERAGE(K26:N26)</f>
         <v>234.98786474999997</v>
       </c>
-      <c r="AA26" s="3">
-        <f>+Z26</f>
+      <c r="AE26" s="3">
+        <f>+AD26</f>
         <v>234.98786474999997</v>
       </c>
-      <c r="AB26" s="3">
-        <f t="shared" ref="AB26:AF26" si="48">+AA26</f>
+      <c r="AF26" s="3">
+        <f t="shared" ref="AF26:AJ26" si="48">+AE26</f>
         <v>234.98786474999997</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AG26" s="3">
         <f t="shared" si="48"/>
         <v>234.98786474999997</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AH26" s="3">
         <f t="shared" si="48"/>
         <v>234.98786474999997</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AI26" s="3">
         <f t="shared" si="48"/>
         <v>234.98786474999997</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AJ26" s="3">
         <f t="shared" si="48"/>
         <v>234.98786474999997</v>
       </c>
     </row>
-    <row r="28" spans="2:119" s="10" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:123" s="10" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B28" s="10" t="s">
         <v>30</v>
       </c>
@@ -3420,72 +3510,76 @@
         <f t="shared" si="49"/>
         <v>0.34015326132365065</v>
       </c>
-      <c r="V28" s="13">
-        <f t="shared" ref="V28:AF28" si="50">+V12/U12-1</f>
+      <c r="S28" s="12"/>
+      <c r="T28" s="12"/>
+      <c r="U28" s="12"/>
+      <c r="V28" s="12"/>
+      <c r="Z28" s="13">
+        <f t="shared" ref="Z28:AJ28" si="50">+Z12/Y12-1</f>
         <v>0.80184839749024928</v>
       </c>
-      <c r="W28" s="13">
+      <c r="AA28" s="13">
         <f t="shared" si="50"/>
         <v>0.8276652527276025</v>
       </c>
-      <c r="X28" s="13">
+      <c r="AB28" s="13">
         <f t="shared" si="50"/>
         <v>0.9380604535857997</v>
       </c>
-      <c r="Y28" s="13">
+      <c r="AC28" s="13">
         <f t="shared" si="50"/>
         <v>0.65491273751413881</v>
       </c>
-      <c r="Z28" s="13">
+      <c r="AD28" s="13">
         <f t="shared" si="50"/>
         <v>0.69325000000000014</v>
       </c>
-      <c r="AA28" s="13">
+      <c r="AE28" s="13">
         <f t="shared" si="50"/>
         <v>0.60540299651747254</v>
       </c>
-      <c r="AB28" s="13">
+      <c r="AF28" s="13">
         <f t="shared" si="50"/>
         <v>0.24725289773877868</v>
       </c>
-      <c r="AC28" s="13">
+      <c r="AG28" s="13">
         <f t="shared" si="50"/>
         <v>0.18157312299496731</v>
       </c>
-      <c r="AD28" s="13">
+      <c r="AH28" s="13">
         <f t="shared" si="50"/>
         <v>0.16212920440259659</v>
       </c>
-      <c r="AE28" s="13">
+      <c r="AI28" s="13">
         <f t="shared" si="50"/>
         <v>0.14710666939536576</v>
       </c>
-      <c r="AF28" s="13">
+      <c r="AJ28" s="13">
         <f t="shared" si="50"/>
         <v>0.13515139759478934</v>
       </c>
-      <c r="AG28" s="13">
-        <f t="shared" ref="AG28" si="51">+AG12/AF12-1</f>
+      <c r="AK28" s="13">
+        <f t="shared" ref="AK28" si="51">+AK12/AJ12-1</f>
         <v>-1</v>
       </c>
-      <c r="AH28" s="13" t="e">
-        <f t="shared" ref="AH28" si="52">+AH12/AG12-1</f>
+      <c r="AL28" s="13" t="e">
+        <f t="shared" ref="AL28" si="52">+AL12/AK12-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI28" s="13" t="e">
-        <f t="shared" ref="AI28" si="53">+AI12/AH12-1</f>
+      <c r="AM28" s="13" t="e">
+        <f t="shared" ref="AM28" si="53">+AM12/AL12-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AJ28" s="13" t="e">
-        <f t="shared" ref="AJ28" si="54">+AJ12/AI12-1</f>
+      <c r="AN28" s="13" t="e">
+        <f t="shared" ref="AN28" si="54">+AN12/AM12-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AK28" s="13" t="e">
-        <f t="shared" ref="AK28" si="55">+AK12/AJ12-1</f>
+      <c r="AO28" s="13" t="e">
+        <f t="shared" ref="AO28" si="55">+AO12/AN12-1</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="29" spans="2:119" s="10" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:123" s="10" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B29" s="10" t="s">
         <v>88</v>
       </c>
@@ -3523,10 +3617,10 @@
       <c r="P29" s="12"/>
       <c r="Q29" s="12"/>
       <c r="R29" s="12"/>
-      <c r="V29" s="13"/>
-      <c r="W29" s="13"/>
-      <c r="X29" s="13"/>
-      <c r="Y29" s="13"/>
+      <c r="S29" s="12"/>
+      <c r="T29" s="12"/>
+      <c r="U29" s="12"/>
+      <c r="V29" s="12"/>
       <c r="Z29" s="13"/>
       <c r="AA29" s="13"/>
       <c r="AB29" s="13"/>
@@ -3534,8 +3628,12 @@
       <c r="AD29" s="13"/>
       <c r="AE29" s="13"/>
       <c r="AF29" s="13"/>
-    </row>
-    <row r="31" spans="2:119" x14ac:dyDescent="0.25">
+      <c r="AG29" s="13"/>
+      <c r="AH29" s="13"/>
+      <c r="AI29" s="13"/>
+      <c r="AJ29" s="13"/>
+    </row>
+    <row r="31" spans="2:123" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
         <v>40</v>
       </c>
@@ -3591,48 +3689,52 @@
         <f t="shared" si="58"/>
         <v>0.79999999999999993</v>
       </c>
-      <c r="W31" s="14">
-        <f>+W14/W12</f>
-        <v>0.7521535394551967</v>
-      </c>
-      <c r="X31" s="14">
-        <f>+X14/X12</f>
-        <v>0.77568720630992416</v>
-      </c>
-      <c r="Y31" s="14">
-        <f>+Y14/Y12</f>
-        <v>0.81989564220183497</v>
-      </c>
-      <c r="Z31" s="14">
-        <f>+Z14/Z12</f>
-        <v>0.79453022456949285</v>
-      </c>
+      <c r="S31" s="16"/>
+      <c r="T31" s="16"/>
+      <c r="U31" s="16"/>
+      <c r="V31" s="16"/>
       <c r="AA31" s="14">
         <f>+AA14/AA12</f>
+        <v>0.7521535394551967</v>
+      </c>
+      <c r="AB31" s="14">
+        <f>+AB14/AB12</f>
+        <v>0.77568720630992416</v>
+      </c>
+      <c r="AC31" s="14">
+        <f>+AC14/AC12</f>
+        <v>0.81989564220183497</v>
+      </c>
+      <c r="AD31" s="14">
+        <f>+AD14/AD12</f>
+        <v>0.79453022456949285</v>
+      </c>
+      <c r="AE31" s="14">
+        <f>+AE14/AE12</f>
         <v>0.78</v>
       </c>
-      <c r="AB31" s="14">
-        <f t="shared" ref="AB31:AF31" si="59">+AB14/AB12</f>
+      <c r="AF31" s="14">
+        <f t="shared" ref="AF31:AJ31" si="59">+AF14/AF12</f>
         <v>0.75000000000000011</v>
       </c>
-      <c r="AC31" s="14">
+      <c r="AG31" s="14">
         <f t="shared" si="59"/>
         <v>0.72</v>
       </c>
-      <c r="AD31" s="14">
+      <c r="AH31" s="14">
         <f t="shared" si="59"/>
         <v>0.7</v>
       </c>
-      <c r="AE31" s="14">
+      <c r="AI31" s="14">
         <f t="shared" si="59"/>
         <v>0.7</v>
       </c>
-      <c r="AF31" s="14">
+      <c r="AJ31" s="14">
         <f t="shared" si="59"/>
         <v>0.7</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B33" s="17" t="s">
         <v>3</v>
       </c>
@@ -3653,7 +3755,7 @@
         <v>301.10699999999997</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B34" s="17" t="s">
         <v>58</v>
       </c>
@@ -3669,18 +3771,18 @@
       <c r="N34" s="5">
         <v>64.427000000000007</v>
       </c>
-      <c r="AA34" s="1">
+      <c r="AE34" s="1">
         <v>0.61</v>
       </c>
-      <c r="AB34" s="1">
+      <c r="AF34" s="1">
         <v>0.88</v>
       </c>
-      <c r="AH34" s="3">
-        <f>NPV(8%,AA24:DO24)</f>
+      <c r="AL34" s="3">
+        <f>NPV(8%,AE24:DS24)</f>
         <v>10184.10144433712</v>
       </c>
     </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B35" s="17" t="s">
         <v>59</v>
       </c>
@@ -3696,12 +3798,12 @@
       <c r="N35" s="5">
         <v>31.152999999999999</v>
       </c>
-      <c r="AH35" s="2">
-        <f>AH34/Main!I3</f>
+      <c r="AL35" s="2">
+        <f>AL34/Main!I3</f>
         <v>45.498959902247904</v>
       </c>
     </row>
-    <row r="36" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B36" s="17" t="s">
         <v>60</v>
       </c>
@@ -3722,7 +3824,7 @@
         <v>156.13799999999998</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B37" s="17" t="s">
         <v>61</v>
       </c>
@@ -3739,7 +3841,7 @@
         <v>82.082999999999998</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B38" s="17" t="s">
         <v>55</v>
       </c>
@@ -3756,7 +3858,7 @@
         <v>10.881</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B39" s="17" t="s">
         <v>62</v>
       </c>
@@ -3773,7 +3875,7 @@
         <v>61.603000000000002</v>
       </c>
     </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B40" s="17" t="s">
         <v>63</v>
       </c>
@@ -3790,7 +3892,7 @@
         <v>0.14699999999999999</v>
       </c>
     </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B41" s="17" t="s">
         <v>57</v>
       </c>
@@ -3811,10 +3913,10 @@
         <v>707.53899999999999</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.25">
       <c r="M42" s="5"/>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B43" s="17" t="s">
         <v>52</v>
       </c>
@@ -3831,7 +3933,7 @@
         <v>91.18</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B44" s="17" t="s">
         <v>53</v>
       </c>
@@ -3848,7 +3950,7 @@
         <v>53.012999999999998</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B45" s="17" t="s">
         <v>54</v>
       </c>
@@ -3865,7 +3967,7 @@
         <v>75.284999999999997</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B46" s="17" t="s">
         <v>64</v>
       </c>
@@ -3882,7 +3984,7 @@
         <v>1.889</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B47" s="17" t="s">
         <v>55</v>
       </c>
@@ -3901,7 +4003,7 @@
         <v>9.4559999999999995</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B48" s="17" t="s">
         <v>56</v>
       </c>
@@ -4202,7 +4304,7 @@
         <v>9.679000000000002</v>
       </c>
     </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B65" s="17" t="s">
         <v>74</v>
       </c>
@@ -4222,7 +4324,7 @@
         <v>-2.3650000000000011</v>
       </c>
     </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B66" s="21" t="s">
         <v>86</v>
       </c>
@@ -4241,7 +4343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B67" s="17" t="s">
         <v>31</v>
       </c>
@@ -4261,7 +4363,7 @@
         <v>-24.52</v>
       </c>
     </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B68" s="17" t="s">
         <v>73</v>
       </c>
@@ -4282,10 +4384,10 @@
         <v>-17.206</v>
       </c>
     </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.25">
       <c r="N69" s="5"/>
     </row>
-    <row r="70" spans="2:34" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:38" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B70" s="20" t="s">
         <v>78</v>
       </c>
@@ -4317,8 +4419,12 @@
       <c r="P70" s="5"/>
       <c r="Q70" s="5"/>
       <c r="R70" s="5"/>
-    </row>
-    <row r="71" spans="2:34" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S70" s="5"/>
+      <c r="T70" s="5"/>
+      <c r="U70" s="5"/>
+      <c r="V70" s="5"/>
+    </row>
+    <row r="71" spans="2:38" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B71" s="20" t="s">
         <v>64</v>
       </c>
@@ -4349,8 +4455,12 @@
       <c r="P71" s="5"/>
       <c r="Q71" s="5"/>
       <c r="R71" s="5"/>
-    </row>
-    <row r="72" spans="2:34" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S71" s="5"/>
+      <c r="T71" s="5"/>
+      <c r="U71" s="5"/>
+      <c r="V71" s="5"/>
+    </row>
+    <row r="72" spans="2:38" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B72" s="20" t="s">
         <v>77</v>
       </c>
@@ -4381,8 +4491,12 @@
       <c r="P72" s="5"/>
       <c r="Q72" s="5"/>
       <c r="R72" s="5"/>
-    </row>
-    <row r="73" spans="2:34" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S72" s="5"/>
+      <c r="T72" s="5"/>
+      <c r="U72" s="5"/>
+      <c r="V72" s="5"/>
+    </row>
+    <row r="73" spans="2:38" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B73" s="20" t="s">
         <v>76</v>
       </c>
@@ -4414,8 +4528,12 @@
       <c r="P73" s="5"/>
       <c r="Q73" s="5"/>
       <c r="R73" s="5"/>
-    </row>
-    <row r="74" spans="2:34" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S73" s="5"/>
+      <c r="T73" s="5"/>
+      <c r="U73" s="5"/>
+      <c r="V73" s="5"/>
+    </row>
+    <row r="74" spans="2:38" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B74" s="20" t="s">
         <v>79</v>
       </c>
@@ -4446,8 +4564,12 @@
       <c r="P74" s="5"/>
       <c r="Q74" s="5"/>
       <c r="R74" s="5"/>
-    </row>
-    <row r="75" spans="2:34" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S74" s="5"/>
+      <c r="T74" s="5"/>
+      <c r="U74" s="5"/>
+      <c r="V74" s="5"/>
+    </row>
+    <row r="75" spans="2:38" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B75" s="20" t="s">
         <v>80</v>
       </c>
@@ -4479,8 +4601,12 @@
       <c r="P75" s="5"/>
       <c r="Q75" s="5"/>
       <c r="R75" s="5"/>
-    </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.25">
+      <c r="S75" s="5"/>
+      <c r="T75" s="5"/>
+      <c r="U75" s="5"/>
+      <c r="V75" s="5"/>
+    </row>
+    <row r="77" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B77" s="1" t="s">
         <v>29</v>
       </c>
@@ -4493,27 +4619,27 @@
       <c r="K77" s="5"/>
       <c r="L77" s="5"/>
       <c r="M77" s="19"/>
-      <c r="AG77" s="17" t="s">
+      <c r="AK77" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="AH77" s="14">
+      <c r="AL77" s="14">
         <v>0.09</v>
       </c>
     </row>
-    <row r="78" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B78" s="1" t="s">
         <v>31</v>
       </c>
       <c r="L78" s="5"/>
       <c r="M78" s="19"/>
-      <c r="AG78" s="17" t="s">
+      <c r="AK78" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="AH78" s="14">
+      <c r="AL78" s="14">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B79" s="1" t="s">
         <v>32</v>
       </c>
@@ -4536,11 +4662,11 @@
       <c r="O79" s="4">
         <v>50</v>
       </c>
-      <c r="AG79" s="17" t="s">
+      <c r="AK79" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="AH79" s="3">
-        <f>NPV(AH77,AA24:DO24)</f>
+      <c r="AL79" s="3">
+        <f>NPV(AL77,AE24:DS24)</f>
         <v>9001.6719167412703</v>
       </c>
     </row>
